--- a/ExcelTable/Enum.xlsx
+++ b/ExcelTable/Enum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevD\TileSystem\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312E0F3D-BF3F-4AC0-8AA0-0BB812C28602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F67E26F-A505-4784-8E8B-2927B1D460B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31380" yWindow="1980" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="1470" windowWidth="22665" windowHeight="12945" tabRatio="894" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumTable" sheetId="17" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>type</t>
   </si>
@@ -98,6 +98,10 @@
   </si>
   <si>
     <t>Decoration</t>
+  </si>
+  <si>
+    <t>DisplayStand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -480,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
@@ -630,6 +634,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
